--- a/diseases/d091/2010-2014.xlsx
+++ b/diseases/d091/2010-2014.xlsx
@@ -1061,9 +1061,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1457,9 +1454,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1605,9 +1599,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -2297,9 +2288,6 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
@@ -2445,9 +2433,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
@@ -3137,9 +3122,6 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
@@ -3285,9 +3267,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -4125,9 +4104,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -4273,9 +4249,6 @@
       <c r="O23" t="n">
         <v>0</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -5113,9 +5086,6 @@
       <c r="O28" t="n">
         <v>0</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
@@ -5261,9 +5231,6 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
@@ -6101,9 +6068,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
@@ -6249,9 +6213,6 @@
       <c r="O35" t="n">
         <v>0</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0</v>
       </c>
@@ -7089,9 +7050,6 @@
       <c r="O40" t="n">
         <v>0</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
@@ -7237,9 +7195,6 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
@@ -7929,9 +7884,6 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
@@ -8077,9 +8029,6 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
@@ -8769,9 +8718,6 @@
       <c r="O50" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
@@ -8917,9 +8863,6 @@
       <c r="O51" t="n">
         <v>1</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0.02045340285308607</v>
       </c>
@@ -9609,9 +9552,6 @@
       <c r="O55" t="n">
         <v>0</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
@@ -9757,9 +9697,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -10449,9 +10386,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
@@ -10597,9 +10531,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -11289,9 +11220,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -11437,9 +11365,6 @@
       <c r="O66" t="n">
         <v>0</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0</v>
       </c>
@@ -12129,9 +12054,6 @@
       <c r="O70" t="n">
         <v>0</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0</v>
       </c>
@@ -12525,9 +12447,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -13117,9 +13036,6 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
@@ -13709,9 +13625,6 @@
       <c r="O80" t="n">
         <v>0</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0</v>
       </c>
@@ -14153,9 +14066,6 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
@@ -14597,9 +14507,6 @@
       <c r="O86" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0</v>
       </c>
@@ -15041,9 +14948,6 @@
       <c r="O89" t="n">
         <v>0</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0</v>
       </c>
@@ -15633,9 +15537,6 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
@@ -16225,9 +16126,6 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
@@ -16669,9 +16567,6 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
@@ -17113,9 +17008,6 @@
       <c r="O103" t="n">
         <v>0</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0</v>
       </c>
@@ -17557,9 +17449,6 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
@@ -18001,9 +17890,6 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
@@ -18445,9 +18331,6 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
@@ -18841,9 +18724,6 @@
       <c r="O114" t="n">
         <v>0</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0</v>
       </c>
@@ -19285,9 +19165,6 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
@@ -19729,9 +19606,6 @@
       <c r="O120" t="n">
         <v>0</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0</v>
       </c>
@@ -20173,9 +20047,6 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0</v>
       </c>
@@ -20617,9 +20488,6 @@
       <c r="O126" t="n">
         <v>0</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0</v>
       </c>
@@ -21061,9 +20929,6 @@
       <c r="O129" t="n">
         <v>0</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0</v>
       </c>
@@ -21505,9 +21370,6 @@
       <c r="O132" t="n">
         <v>0</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0</v>
       </c>
@@ -21949,9 +21811,6 @@
       <c r="O135" t="n">
         <v>0</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0</v>
       </c>
@@ -22393,9 +22252,6 @@
       <c r="O138" t="n">
         <v>0</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0</v>
       </c>
@@ -23281,9 +23137,6 @@
       <c r="O144" t="n">
         <v>0</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0</v>
       </c>
@@ -24317,9 +24170,6 @@
       <c r="O151" t="n">
         <v>0</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0</v>
       </c>
@@ -25501,9 +25351,6 @@
       <c r="O159" t="n">
         <v>0</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0</v>
       </c>
@@ -26685,9 +26532,6 @@
       <c r="O167" t="n">
         <v>0</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>0</v>
       </c>
@@ -27081,9 +26925,6 @@
       <c r="O169" t="n">
         <v>0</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>0</v>
       </c>
@@ -27229,9 +27070,6 @@
       <c r="O170" t="n">
         <v>0</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0</v>
       </c>
@@ -28661,9 +28499,6 @@
       <c r="O179" t="n">
         <v>0</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>0</v>
       </c>
@@ -28809,9 +28644,6 @@
       <c r="O180" t="n">
         <v>0</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0</v>
       </c>
@@ -30093,9 +29925,6 @@
       <c r="O188" t="n">
         <v>0</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>0</v>
       </c>
@@ -30241,9 +30070,6 @@
       <c r="O189" t="n">
         <v>0</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0</v>
       </c>
@@ -31525,9 +31351,6 @@
       <c r="O197" t="n">
         <v>0</v>
       </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
       <c r="R197" t="n">
         <v>0</v>
       </c>
@@ -31673,9 +31496,6 @@
       <c r="O198" t="n">
         <v>0</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0</v>
       </c>
@@ -32957,9 +32777,6 @@
       <c r="O206" t="n">
         <v>0</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>0</v>
       </c>
@@ -33105,9 +32922,6 @@
       <c r="O207" t="n">
         <v>0</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="R207" t="n">
         <v>0</v>
       </c>
@@ -34537,9 +34351,6 @@
       <c r="O216" t="n">
         <v>0</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="R216" t="n">
         <v>0</v>
       </c>
@@ -34685,9 +34496,6 @@
       <c r="O217" t="n">
         <v>0</v>
       </c>
-      <c r="Q217" t="n">
-        <v>0</v>
-      </c>
       <c r="R217" t="n">
         <v>0</v>
       </c>
@@ -35969,9 +35777,6 @@
       <c r="O225" t="n">
         <v>0</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="R225" t="n">
         <v>0</v>
       </c>
@@ -36117,9 +35922,6 @@
       <c r="O226" t="n">
         <v>0</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="R226" t="n">
         <v>0</v>
       </c>
@@ -37401,9 +37203,6 @@
       <c r="O234" t="n">
         <v>0</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="R234" t="n">
         <v>0</v>
       </c>
@@ -37549,9 +37348,6 @@
       <c r="O235" t="n">
         <v>1</v>
       </c>
-      <c r="Q235" t="n">
-        <v>0</v>
-      </c>
       <c r="R235" t="n">
         <v>0.01968455694343711</v>
       </c>
@@ -39129,9 +38925,6 @@
       <c r="O245" t="n">
         <v>0</v>
       </c>
-      <c r="Q245" t="n">
-        <v>0</v>
-      </c>
       <c r="R245" t="n">
         <v>0</v>
       </c>
@@ -39277,9 +39070,6 @@
       <c r="O246" t="n">
         <v>0</v>
       </c>
-      <c r="Q246" t="n">
-        <v>0</v>
-      </c>
       <c r="R246" t="n">
         <v>0</v>
       </c>
@@ -40561,9 +40351,6 @@
       <c r="O254" t="n">
         <v>0</v>
       </c>
-      <c r="Q254" t="n">
-        <v>0</v>
-      </c>
       <c r="R254" t="n">
         <v>0</v>
       </c>
@@ -40709,9 +40496,6 @@
       <c r="O255" t="n">
         <v>6</v>
       </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
       <c r="R255" t="n">
         <v>0.1181073416606227</v>
       </c>
@@ -42141,9 +41925,6 @@
       <c r="O264" t="n">
         <v>0</v>
       </c>
-      <c r="Q264" t="n">
-        <v>0</v>
-      </c>
       <c r="R264" t="n">
         <v>0</v>
       </c>
@@ -42289,9 +42070,6 @@
       <c r="O265" t="n">
         <v>1</v>
       </c>
-      <c r="Q265" t="n">
-        <v>0</v>
-      </c>
       <c r="R265" t="n">
         <v>0.01968455694343711</v>
       </c>
@@ -43573,9 +43351,6 @@
       <c r="O273" t="n">
         <v>0</v>
       </c>
-      <c r="Q273" t="n">
-        <v>0</v>
-      </c>
       <c r="R273" t="n">
         <v>0</v>
       </c>
@@ -43721,9 +43496,6 @@
       <c r="O274" t="n">
         <v>0</v>
       </c>
-      <c r="Q274" t="n">
-        <v>0</v>
-      </c>
       <c r="R274" t="n">
         <v>0</v>
       </c>
@@ -45301,9 +45073,6 @@
       <c r="O284" t="n">
         <v>0</v>
       </c>
-      <c r="Q284" t="n">
-        <v>0</v>
-      </c>
       <c r="R284" t="n">
         <v>0</v>
       </c>
@@ -45697,9 +45466,6 @@
       <c r="O286" t="n">
         <v>0</v>
       </c>
-      <c r="Q286" t="n">
-        <v>0</v>
-      </c>
       <c r="R286" t="n">
         <v>0</v>
       </c>
@@ -45845,9 +45611,6 @@
       <c r="O287" t="n">
         <v>1</v>
       </c>
-      <c r="Q287" t="n">
-        <v>0</v>
-      </c>
       <c r="R287" t="n">
         <v>0.01946511802187685</v>
       </c>
@@ -47425,9 +47188,6 @@
       <c r="O297" t="n">
         <v>0</v>
       </c>
-      <c r="Q297" t="n">
-        <v>0</v>
-      </c>
       <c r="R297" t="n">
         <v>0</v>
       </c>
@@ -47573,9 +47333,6 @@
       <c r="O298" t="n">
         <v>0</v>
       </c>
-      <c r="Q298" t="n">
-        <v>0</v>
-      </c>
       <c r="R298" t="n">
         <v>0</v>
       </c>
@@ -49005,9 +48762,6 @@
       <c r="O307" t="n">
         <v>0</v>
       </c>
-      <c r="Q307" t="n">
-        <v>0</v>
-      </c>
       <c r="R307" t="n">
         <v>0</v>
       </c>
@@ -49153,9 +48907,6 @@
       <c r="O308" t="n">
         <v>0</v>
       </c>
-      <c r="Q308" t="n">
-        <v>0</v>
-      </c>
       <c r="R308" t="n">
         <v>0</v>
       </c>
@@ -50585,9 +50336,6 @@
       <c r="O317" t="n">
         <v>0</v>
       </c>
-      <c r="Q317" t="n">
-        <v>0</v>
-      </c>
       <c r="R317" t="n">
         <v>0</v>
       </c>
@@ -50733,9 +50481,6 @@
       <c r="O318" t="n">
         <v>0</v>
       </c>
-      <c r="Q318" t="n">
-        <v>0</v>
-      </c>
       <c r="R318" t="n">
         <v>0</v>
       </c>
@@ -52165,9 +51910,6 @@
       <c r="O327" t="n">
         <v>0</v>
       </c>
-      <c r="Q327" t="n">
-        <v>0</v>
-      </c>
       <c r="R327" t="n">
         <v>0</v>
       </c>
@@ -52313,9 +52055,6 @@
       <c r="O328" t="n">
         <v>0</v>
       </c>
-      <c r="Q328" t="n">
-        <v>0</v>
-      </c>
       <c r="R328" t="n">
         <v>0</v>
       </c>
@@ -53893,9 +53632,6 @@
       <c r="O338" t="n">
         <v>0</v>
       </c>
-      <c r="Q338" t="n">
-        <v>0</v>
-      </c>
       <c r="R338" t="n">
         <v>0</v>
       </c>
@@ -54041,9 +53777,6 @@
       <c r="O339" t="n">
         <v>0</v>
       </c>
-      <c r="Q339" t="n">
-        <v>0</v>
-      </c>
       <c r="R339" t="n">
         <v>0</v>
       </c>
@@ -55473,9 +55206,6 @@
       <c r="O348" t="n">
         <v>0</v>
       </c>
-      <c r="Q348" t="n">
-        <v>0</v>
-      </c>
       <c r="R348" t="n">
         <v>0</v>
       </c>
@@ -55621,9 +55351,6 @@
       <c r="O349" t="n">
         <v>1</v>
       </c>
-      <c r="Q349" t="n">
-        <v>0</v>
-      </c>
       <c r="R349" t="n">
         <v>0.01946511802187685</v>
       </c>
@@ -57201,9 +56928,6 @@
       <c r="O359" t="n">
         <v>0</v>
       </c>
-      <c r="Q359" t="n">
-        <v>0</v>
-      </c>
       <c r="R359" t="n">
         <v>0</v>
       </c>
@@ -57349,9 +57073,6 @@
       <c r="O360" t="n">
         <v>0</v>
       </c>
-      <c r="Q360" t="n">
-        <v>0</v>
-      </c>
       <c r="R360" t="n">
         <v>0</v>
       </c>
@@ -58781,9 +58502,6 @@
       <c r="O369" t="n">
         <v>1</v>
       </c>
-      <c r="Q369" t="n">
-        <v>0</v>
-      </c>
       <c r="R369" t="n">
         <v>0.001978667765170246</v>
       </c>
@@ -58929,9 +58647,6 @@
       <c r="O370" t="n">
         <v>0</v>
       </c>
-      <c r="Q370" t="n">
-        <v>0</v>
-      </c>
       <c r="R370" t="n">
         <v>0</v>
       </c>
@@ -60361,9 +60076,6 @@
       <c r="O379" t="n">
         <v>0</v>
       </c>
-      <c r="Q379" t="n">
-        <v>0</v>
-      </c>
       <c r="R379" t="n">
         <v>0</v>
       </c>
@@ -60509,9 +60221,6 @@
       <c r="O380" t="n">
         <v>0</v>
       </c>
-      <c r="Q380" t="n">
-        <v>0</v>
-      </c>
       <c r="R380" t="n">
         <v>0</v>
       </c>
@@ -62089,9 +61798,6 @@
       <c r="O390" t="n">
         <v>0</v>
       </c>
-      <c r="Q390" t="n">
-        <v>0</v>
-      </c>
       <c r="R390" t="n">
         <v>0</v>
       </c>
@@ -62237,9 +61943,6 @@
       <c r="O391" t="n">
         <v>1</v>
       </c>
-      <c r="Q391" t="n">
-        <v>0</v>
-      </c>
       <c r="R391" t="n">
         <v>0.01946511802187685</v>
       </c>
@@ -63669,9 +63372,6 @@
       <c r="O400" t="n">
         <v>0</v>
       </c>
-      <c r="Q400" t="n">
-        <v>0</v>
-      </c>
       <c r="R400" t="n">
         <v>0</v>
       </c>
@@ -63816,9 +63516,6 @@
       </c>
       <c r="O401" t="n">
         <v>1</v>
-      </c>
-      <c r="Q401" t="n">
-        <v>0</v>
       </c>
       <c r="R401" t="n">
         <v>0.01946511802187685</v>
